--- a/backend-auditor/templates/quadro_07.xlsx
+++ b/backend-auditor/templates/quadro_07.xlsx
@@ -681,17 +681,17 @@
       <c r="B5" s="17" t="n"/>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Até o 1º Quadrimestre</t>
+          <t>{rotulos.col_1}</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Até o 2º Quadrimestre</t>
+          <t>{rotulos.col_2}</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Até o 3º Quadrimestre</t>
+          <t>{rotulos.col_3}</t>
         </is>
       </c>
     </row>
